--- a/raw_datas/buoy/1-堺/堺.xlsx
+++ b/raw_datas/buoy/1-堺/堺.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10302"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tokudashintaro/Desktop/LDA_PP/raw_datas/buoy/1-堺/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tokudashintarou/Desktop/LDA_PP/raw_datas/buoy/1-堺/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7F8BC7F-AEDA-8A44-9710-8163CE9012A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAA94007-8067-3142-89B3-E8A0FEEFA088}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="堺" sheetId="1" r:id="rId1"/>
@@ -477,6 +477,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="9" max="9" width="30.5" customWidth="1"/>
+    <col min="10" max="10" width="52.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">

--- a/raw_datas/buoy/1-堺/堺.xlsx
+++ b/raw_datas/buoy/1-堺/堺.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10419"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tokudashintarou/Desktop/LDA_PP/raw_datas/buoy/1-堺/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAA94007-8067-3142-89B3-E8A0FEEFA088}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3B79FF1-370C-8247-9F91-13B0922B6E24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="堺" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
